--- a/港岛-西营盘及上环-尚逸/尚逸_销控明细表.xlsx
+++ b/港岛-西营盘及上环-尚逸/尚逸_销控明细表.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -116,12 +116,6 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
@@ -202,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -261,10 +255,7 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -945,38 +936,30 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>26280600</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>40999</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K6" s="5" t="n">
+        <v>26280600</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>40999</v>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
@@ -985,7 +968,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -10798,7 +10781,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -10808,7 +10791,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>161</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -10873,12 +10856,12 @@
       <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 641呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C5" s="21" t="inlineStr">
+$2628万
+$40,999/呎
+(26年-07月-26日)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 666呎 (3房)
 $2800万
@@ -10886,10 +10869,10 @@
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr"/>
-      <c r="E5" s="22" t="inlineStr"/>
-      <c r="F5" s="22" t="inlineStr"/>
-      <c r="G5" s="21" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $850万
@@ -10897,7 +10880,7 @@
 (26年-01月-28日)</t>
         </is>
       </c>
-      <c r="H5" s="21" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $830万
@@ -10912,7 +10895,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 492呎 (3房)
 $1499万
@@ -10920,7 +10903,7 @@
 (25年-08月-14日)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 344呎 (1房)
 $982万
@@ -10928,7 +10911,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 474呎 (3房)
 $1397万
@@ -10936,9 +10919,9 @@
 (25年-08月-27日)</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr"/>
-      <c r="F6" s="22" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $749万
@@ -10946,7 +10929,7 @@
 (25年-08月-14日)</t>
         </is>
       </c>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $723万
@@ -10961,7 +10944,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 492呎 (3房)
 $1386万
@@ -10969,7 +10952,7 @@
 (25年-08月-03日)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 344呎 (1房)
 $900万
@@ -10977,7 +10960,7 @@
 (24年-10月-22日)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 474呎 (3房)
 $1294万
@@ -10985,9 +10968,9 @@
 (25年-08月-21日)</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr"/>
-      <c r="F7" s="22" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $736万
@@ -10995,7 +10978,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $691万
@@ -11010,7 +10993,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 492呎 (3房)
 $1304万
@@ -11018,7 +11001,7 @@
 (24年-09月-03日)</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 344呎 (1房)
 $896万
@@ -11026,7 +11009,7 @@
 (25年-08月-14日)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 474呎 (3房)
 $1266万
@@ -11034,9 +11017,9 @@
 (25年-08月-12日)</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr"/>
-      <c r="F8" s="22" t="inlineStr"/>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr"/>
+      <c r="F8" s="21" t="inlineStr"/>
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $705万
@@ -11044,7 +11027,7 @@
 (25年-05月-11日)</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $733万
@@ -11059,7 +11042,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 492呎 (3房)
 $1259万
@@ -11067,7 +11050,7 @@
 (24年-07月-18日)</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 344呎 (1房)
 $883万
@@ -11075,7 +11058,7 @@
 (25年-08月-14日)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 474呎 (3房)
 $1194万
@@ -11083,9 +11066,9 @@
 (24年-07月-23日)</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr"/>
-      <c r="F9" s="22" t="inlineStr"/>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr"/>
+      <c r="F9" s="21" t="inlineStr"/>
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $695万
@@ -11093,7 +11076,7 @@
 (25年-04月-01日)</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $663万
@@ -11108,7 +11091,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $973万
@@ -11116,7 +11099,7 @@
 (24年-07月-23日)</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $660万
@@ -11124,7 +11107,7 @@
 (24年-07月-30日)</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $537万
@@ -11132,7 +11115,7 @@
 (25年-03月-05日)</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $729万
@@ -11140,7 +11123,7 @@
 (24年-12月-12日)</t>
         </is>
       </c>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $486万
@@ -11148,7 +11131,7 @@
 (24年-10月-28日)</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $656万
@@ -11156,7 +11139,7 @@
 (24年-09月-24日)</t>
         </is>
       </c>
-      <c r="H10" s="21" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $620万
@@ -11171,7 +11154,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $1101万
@@ -11179,7 +11162,7 @@
 (25年-07月-30日)</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $650万
@@ -11187,7 +11170,7 @@
 (24年-08月-26日)</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $525万
@@ -11195,7 +11178,7 @@
 (25年-04月-21日)</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $711万
@@ -11203,7 +11186,7 @@
 (24年-11月-28日)</t>
         </is>
       </c>
-      <c r="F11" s="21" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $481万
@@ -11211,7 +11194,7 @@
 (24年-11月-03日)</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $646万
@@ -11219,7 +11202,7 @@
 (24年-09月-23日)</t>
         </is>
       </c>
-      <c r="H11" s="21" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $618万
@@ -11234,7 +11217,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $989万
@@ -11242,7 +11225,7 @@
 (24年-09月-11日)</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $691万
@@ -11250,7 +11233,7 @@
 (24年-08月-27日)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $520万
@@ -11258,7 +11241,7 @@
 (25年-03月-27日)</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $686万
@@ -11266,7 +11249,7 @@
 (24年-09月-23日)</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $476万
@@ -11274,7 +11257,7 @@
 (24年-10月-20日)</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $630万
@@ -11282,7 +11265,7 @@
 (24年-08月-15日)</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $601万
@@ -11297,7 +11280,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $900万
@@ -11305,7 +11288,7 @@
 (24年-07月-23日)</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $625万
@@ -11313,7 +11296,7 @@
 (24年-09月-08日)</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $507万
@@ -11321,7 +11304,7 @@
 (24年-12月-26日)</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $708万
@@ -11329,7 +11312,7 @@
 (24年-08月-19日)</t>
         </is>
       </c>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $466万
@@ -11337,7 +11320,7 @@
 (24年-08月-27日)</t>
         </is>
       </c>
-      <c r="G13" s="21" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $620万
@@ -11345,7 +11328,7 @@
 (24年-09月-01日)</t>
         </is>
       </c>
-      <c r="H13" s="21" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $600万
@@ -11360,7 +11343,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $883万
@@ -11368,7 +11351,7 @@
 (24年-07月-18日)</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $670万
@@ -11376,7 +11359,7 @@
 (24年-10月-06日)</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $498万
@@ -11384,7 +11367,7 @@
 (25年-04月-02日)</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $621万
@@ -11392,7 +11375,7 @@
 (24年-09月-18日)</t>
         </is>
       </c>
-      <c r="F14" s="21" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $466万
@@ -11400,7 +11383,7 @@
 (24年-10月-13日)</t>
         </is>
       </c>
-      <c r="G14" s="21" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $607万
@@ -11408,7 +11391,7 @@
 (24年-08月-08日)</t>
         </is>
       </c>
-      <c r="H14" s="21" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $597万
@@ -11423,7 +11406,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $870万
@@ -11431,7 +11414,7 @@
 (24年-07月-21日)</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $620万
@@ -11439,7 +11422,7 @@
 (24年-10月-01日)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $495万
@@ -11447,7 +11430,7 @@
 (25年-02月-16日)</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $590万
@@ -11455,7 +11438,7 @@
 (24年-08月-20日)</t>
         </is>
       </c>
-      <c r="F15" s="21" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $455万
@@ -11463,7 +11446,7 @@
 (24年-10月-08日)</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $598万
@@ -11471,7 +11454,7 @@
 (24年-07月-23日)</t>
         </is>
       </c>
-      <c r="H15" s="21" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $581万
@@ -11486,7 +11469,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $857万
@@ -11494,7 +11477,7 @@
 (24年-07月-25日)</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $574万
@@ -11502,7 +11485,7 @@
 (24年-08月-26日)</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $500万
@@ -11510,7 +11493,7 @@
 (25年-01月-12日)</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $602万
@@ -11518,7 +11501,7 @@
 (24年-09月-11日)</t>
         </is>
       </c>
-      <c r="F16" s="21" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $445万
@@ -11526,7 +11509,7 @@
 (24年-08月-28日)</t>
         </is>
       </c>
-      <c r="G16" s="21" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $576万
@@ -11534,7 +11517,7 @@
 (24年-07月-23日)</t>
         </is>
       </c>
-      <c r="H16" s="21" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $575万
@@ -11549,7 +11532,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $845万
@@ -11557,7 +11540,7 @@
 (24年-07月-17日)</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $566万
@@ -11565,7 +11548,7 @@
 (24年-07月-18日)</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $528万
@@ -11573,7 +11556,7 @@
 (24年-11月-14日)</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $623万
@@ -11581,7 +11564,7 @@
 (24年-07月-21日)</t>
         </is>
       </c>
-      <c r="F17" s="21" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $448万
@@ -11589,7 +11572,7 @@
 (24年-08月-06日)</t>
         </is>
       </c>
-      <c r="G17" s="21" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $614万
@@ -11597,7 +11580,7 @@
 (24年-07月-21日)</t>
         </is>
       </c>
-      <c r="H17" s="21" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $569万
@@ -11612,7 +11595,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $832万
@@ -11620,7 +11603,7 @@
 (24年-07月-18日)</t>
         </is>
       </c>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $554万
@@ -11628,7 +11611,7 @@
 (24年-07月-28日)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $523万
@@ -11636,7 +11619,7 @@
 (24年-11月-14日)</t>
         </is>
       </c>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $572万
@@ -11644,7 +11627,7 @@
 (24年-08月-08日)</t>
         </is>
       </c>
-      <c r="F18" s="21" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $436万
@@ -11652,7 +11635,7 @@
 (24年-08月-05日)</t>
         </is>
       </c>
-      <c r="G18" s="21" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $564万
@@ -11660,7 +11643,7 @@
 (24年-07月-18日)</t>
         </is>
       </c>
-      <c r="H18" s="21" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $607万
@@ -11675,7 +11658,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $820万
@@ -11683,7 +11666,7 @@
 (24年-07月-25日)</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $548万
@@ -11691,7 +11674,7 @@
 (24年-07月-29日)</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $481万
@@ -11699,7 +11682,7 @@
 (24年-11月-06日)</t>
         </is>
       </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $610万
@@ -11707,7 +11690,7 @@
 (24年-07月-22日)</t>
         </is>
       </c>
-      <c r="F19" s="21" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $438万
@@ -11715,7 +11698,7 @@
 (24年-09月-03日)</t>
         </is>
       </c>
-      <c r="G19" s="21" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $558万
@@ -11723,7 +11706,7 @@
 (24年-07月-18日)</t>
         </is>
       </c>
-      <c r="H19" s="21" t="inlineStr">
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $601万
@@ -11738,7 +11721,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $870万
@@ -11746,7 +11729,7 @@
 (24年-07月-28日)</t>
         </is>
       </c>
-      <c r="C20" s="21" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $543万
@@ -11754,7 +11737,7 @@
 (24年-07月-21日)</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $478万
@@ -11762,7 +11745,7 @@
 (24年-10月-27日)</t>
         </is>
       </c>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $560万
@@ -11770,7 +11753,7 @@
 (24年-07月-24日)</t>
         </is>
       </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $439万
@@ -11778,7 +11761,7 @@
 (24年-07月-23日)</t>
         </is>
       </c>
-      <c r="G20" s="21" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $552万
@@ -11786,7 +11769,7 @@
 (24年-07月-22日)</t>
         </is>
       </c>
-      <c r="H20" s="21" t="inlineStr">
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $555万
@@ -11801,7 +11784,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $796万
@@ -11809,7 +11792,7 @@
 (24年-07月-17日)</t>
         </is>
       </c>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $532万
@@ -11817,7 +11800,7 @@
 (24年-07月-21日)</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $459万
@@ -11825,7 +11808,7 @@
 (24年-09月-18日)</t>
         </is>
       </c>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $548万
@@ -11833,7 +11816,7 @@
 (24年-07月-28日)</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $425万
@@ -11841,7 +11824,7 @@
 (24年-07月-18日)</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $541万
@@ -11849,7 +11832,7 @@
 (24年-07月-23日)</t>
         </is>
       </c>
-      <c r="H21" s="21" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $544万
@@ -11864,7 +11847,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $790万
@@ -11872,7 +11855,7 @@
 (24年-07月-22日)</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $572万
@@ -11880,7 +11863,7 @@
 (24年-07月-29日)</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $438万
@@ -11888,7 +11871,7 @@
 (24年-08月-13日)</t>
         </is>
       </c>
-      <c r="E22" s="21" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $543万
@@ -11896,7 +11879,7 @@
 (24年-07月-21日)</t>
         </is>
       </c>
-      <c r="F22" s="21" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $426万
@@ -11904,7 +11887,7 @@
 (24年-07月-17日)</t>
         </is>
       </c>
-      <c r="G22" s="21" t="inlineStr">
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $540万
@@ -11912,7 +11895,7 @@
 (24年-07月-22日)</t>
         </is>
       </c>
-      <c r="H22" s="21" t="inlineStr">
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $577万
@@ -11927,7 +11910,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $824万
@@ -11935,7 +11918,7 @@
 (24年-08月-11日)</t>
         </is>
       </c>
-      <c r="C23" s="21" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $525万
@@ -11943,7 +11926,7 @@
 (24年-07月-29日)</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $426万
@@ -11951,7 +11934,7 @@
 (24年-07月-29日)</t>
         </is>
       </c>
-      <c r="E23" s="21" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $545万
@@ -11959,7 +11942,7 @@
 (24年-07月-22日)</t>
         </is>
       </c>
-      <c r="F23" s="21" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $444万
@@ -11967,7 +11950,7 @@
 (24年-07月-25日)</t>
         </is>
       </c>
-      <c r="G23" s="21" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $536万
@@ -11975,7 +11958,7 @@
 (24年-07月-22日)</t>
         </is>
       </c>
-      <c r="H23" s="21" t="inlineStr">
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $573万
@@ -11990,7 +11973,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $809万
@@ -11998,7 +11981,7 @@
 (24年-08月-13日)</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $521万
@@ -12006,7 +11989,7 @@
 (24年-07月-21日)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $423万
@@ -12014,7 +11997,7 @@
 (24年-07月-24日)</t>
         </is>
       </c>
-      <c r="E24" s="21" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $538万
@@ -12022,7 +12005,7 @@
 (24年-07月-22日)</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $415万
@@ -12030,7 +12013,7 @@
 (24年-07月-22日)</t>
         </is>
       </c>
-      <c r="G24" s="21" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $531万
@@ -12038,7 +12021,7 @@
 (24年-07月-18日)</t>
         </is>
       </c>
-      <c r="H24" s="21" t="inlineStr">
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $537万
@@ -12053,7 +12036,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $786万
@@ -12061,7 +12044,7 @@
 (24年-07月-24日)</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $517万
@@ -12069,7 +12052,7 @@
 (24年-07月-25日)</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $419万
@@ -12077,7 +12060,7 @@
 (24年-07月-31日)</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $530万
@@ -12085,7 +12068,7 @@
 (24年-07月-30日)</t>
         </is>
       </c>
-      <c r="F25" s="21" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $405万
@@ -12093,7 +12076,7 @@
 (24年-07月-28日)</t>
         </is>
       </c>
-      <c r="G25" s="21" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $515万
@@ -12101,7 +12084,7 @@
 (24年-07月-25日)</t>
         </is>
       </c>
-      <c r="H25" s="21" t="inlineStr">
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $524万
@@ -12116,7 +12099,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $764万
@@ -12124,7 +12107,7 @@
 (24年-07月-17日)</t>
         </is>
       </c>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $543万
@@ -12132,7 +12115,7 @@
 (24年-07月-17日)</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $418万
@@ -12140,7 +12123,7 @@
 (24年-07月-22日)</t>
         </is>
       </c>
-      <c r="E26" s="21" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $518万
@@ -12148,7 +12131,7 @@
 (24年-07月-23日)</t>
         </is>
       </c>
-      <c r="F26" s="21" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $401万
@@ -12156,7 +12139,7 @@
 (24年-07月-28日)</t>
         </is>
       </c>
-      <c r="G26" s="21" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $509万
@@ -12164,7 +12147,7 @@
 (24年-07月-21日)</t>
         </is>
       </c>
-      <c r="H26" s="21" t="inlineStr">
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $513万
@@ -12179,7 +12162,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $749万
@@ -12187,7 +12170,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $538万
@@ -12195,7 +12178,7 @@
 (24年-07月-21日)</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $450万
@@ -12203,7 +12186,7 @@
 (24年-10月-29日)</t>
         </is>
       </c>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $553万
@@ -12211,7 +12194,7 @@
 (24年-07月-24日)</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $422万
@@ -12219,7 +12202,7 @@
 (24年-09月-19日)</t>
         </is>
       </c>
-      <c r="G27" s="21" t="inlineStr">
+      <c r="G27" s="20" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $508万
@@ -12227,7 +12210,7 @@
 (24年-07月-18日)</t>
         </is>
       </c>
-      <c r="H27" s="21" t="inlineStr">
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $504万
@@ -12242,7 +12225,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $720万
@@ -12250,7 +12233,7 @@
 (24年-07月-21日)</t>
         </is>
       </c>
-      <c r="C28" s="21" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $486万
@@ -12258,7 +12241,7 @@
 (24年-07月-23日)</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $403万
@@ -12266,7 +12249,7 @@
 (24年-07月-23日)</t>
         </is>
       </c>
-      <c r="E28" s="21" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $494万
@@ -12274,7 +12257,7 @@
 (24年-07月-17日)</t>
         </is>
       </c>
-      <c r="F28" s="21" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $411万
@@ -12282,8 +12265,8 @@
 (24年-07月-18日)</t>
         </is>
       </c>
-      <c r="G28" s="22" t="inlineStr"/>
-      <c r="H28" s="21" t="inlineStr">
+      <c r="G28" s="21" t="inlineStr"/>
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>G | 277呎 (1房)
 $497万
@@ -12298,7 +12281,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B29" s="21" t="inlineStr">
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>A | 351呎 (2房)
 $869万
@@ -12306,7 +12289,7 @@
 (24年-09月-03日)</t>
         </is>
       </c>
-      <c r="C29" s="21" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>B | 231呎 (1房)
 $515万
@@ -12314,7 +12297,7 @@
 (24年-08月-13日)</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr">
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>C | 177呎 (开放式)
 $400万
@@ -12322,7 +12305,7 @@
 (25年-04月-07日)</t>
         </is>
       </c>
-      <c r="E29" s="21" t="inlineStr">
+      <c r="E29" s="20" t="inlineStr">
         <is>
           <t>D | 254呎 (1房)
 $533万
@@ -12330,9 +12313,9 @@
 (24年-08月-06日)</t>
         </is>
       </c>
-      <c r="F29" s="22" t="inlineStr"/>
-      <c r="G29" s="22" t="inlineStr"/>
-      <c r="H29" s="21" t="inlineStr">
+      <c r="F29" s="21" t="inlineStr"/>
+      <c r="G29" s="21" t="inlineStr"/>
+      <c r="H29" s="20" t="inlineStr">
         <is>
           <t>G | 236呎 (1房)
 $534万
